--- a/results/fptl_johnson.xlsx
+++ b/results/fptl_johnson.xlsx
@@ -470,28 +470,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0203999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0199999999999999</v>
+        <v>0.0196</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0845999999999999</v>
+        <v>0.08099999999999991</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0891999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4574999999999999</v>
+        <v>0.4444</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4547999999999999</v>
+        <v>0.4442</v>
       </c>
       <c r="H2" t="n">
-        <v>45.43329999999999</v>
+        <v>44.8304</v>
       </c>
       <c r="I2" t="n">
-        <v>45.3034</v>
+        <v>44.1047</v>
       </c>
     </row>
     <row r="3">
@@ -499,28 +499,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>0.0238999999999999</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.0226999999999999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.022</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.0697</v>
+        <v>0.0654</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0596</v>
+        <v>0.0643</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3054</v>
+        <v>0.2803</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2871</v>
+        <v>0.2771</v>
       </c>
       <c r="H3" t="n">
-        <v>24.2991</v>
+        <v>23.1787</v>
       </c>
       <c r="I3" t="n">
-        <v>24.2172</v>
+        <v>23.5675</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0215999999999999</v>
+        <v>0.0248</v>
       </c>
       <c r="C4" t="n">
-        <v>0.022</v>
+        <v>0.0253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0677</v>
+        <v>0.0636</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06499999999999991</v>
+        <v>0.0607</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2387999999999999</v>
+        <v>0.2957000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2438</v>
+        <v>0.2692</v>
       </c>
       <c r="H4" t="n">
-        <v>18.4979</v>
+        <v>23.2278</v>
       </c>
       <c r="I4" t="n">
-        <v>18.4816</v>
+        <v>23.11000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0251</v>
+        <v>0.0249</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0238999999999999</v>
+        <v>0.0235999999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0.0638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0608999999999999</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2182</v>
+        <v>0.2216</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2145999999999999</v>
+        <v>0.2188</v>
       </c>
       <c r="H5" t="n">
-        <v>13.2977</v>
+        <v>12.7861</v>
       </c>
       <c r="I5" t="n">
-        <v>13.2293</v>
+        <v>12.6588</v>
       </c>
     </row>
     <row r="6">
@@ -586,28 +586,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0259</v>
+        <v>0.0254</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0249</v>
+        <v>0.027</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0633999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2333999999999999</v>
+        <v>0.2349</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2274</v>
+        <v>0.2236</v>
       </c>
       <c r="H6" t="n">
-        <v>14.3716</v>
+        <v>14.3111</v>
       </c>
       <c r="I6" t="n">
-        <v>14.0806</v>
+        <v>13.9925</v>
       </c>
     </row>
     <row r="7">
@@ -615,28 +615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0276</v>
+        <v>0.0294</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0288</v>
+        <v>0.0293</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0639</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0697</v>
+        <v>0.0668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2423</v>
+        <v>0.2338</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2196</v>
+        <v>0.2459</v>
       </c>
       <c r="H7" t="n">
-        <v>15.6926</v>
+        <v>15.5018</v>
       </c>
       <c r="I7" t="n">
-        <v>14.9732</v>
+        <v>15.2159</v>
       </c>
     </row>
     <row r="8">
@@ -644,28 +644,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0262</v>
+        <v>0.0326</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0257</v>
+        <v>0.0308</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0731</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0729999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2291</v>
+        <v>0.2112</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2195999999999999</v>
+        <v>0.2171</v>
       </c>
       <c r="H8" t="n">
-        <v>16.7594</v>
+        <v>16.5643</v>
       </c>
       <c r="I8" t="n">
-        <v>16.5322</v>
+        <v>16.1353</v>
       </c>
     </row>
     <row r="9">
@@ -673,28 +673,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0279</v>
+        <v>0.0263</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0289</v>
+        <v>0.0293</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0745999999999999</v>
+        <v>0.0766</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0708</v>
+        <v>0.0687</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2193999999999999</v>
+        <v>0.229</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2338</v>
+        <v>0.2259</v>
       </c>
       <c r="H9" t="n">
-        <v>13.3162</v>
+        <v>12.747</v>
       </c>
       <c r="I9" t="n">
-        <v>13.0736</v>
+        <v>12.7497</v>
       </c>
     </row>
     <row r="10">
@@ -702,28 +702,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0312</v>
+        <v>0.0322</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0301</v>
+        <v>0.0332</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0738</v>
+        <v>0.07859999999999991</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2352</v>
+        <v>0.2217</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2355</v>
+        <v>0.2257</v>
       </c>
       <c r="H10" t="n">
-        <v>13.591</v>
+        <v>13.0256</v>
       </c>
       <c r="I10" t="n">
-        <v>13.6774</v>
+        <v>13.0348</v>
       </c>
     </row>
     <row r="11">
@@ -731,28 +731,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0302</v>
+        <v>0.0361999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0319</v>
+        <v>0.0356999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0849999999999999</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0789999999999999</v>
+        <v>0.08159999999999989</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2373</v>
+        <v>0.2312</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2281999999999999</v>
+        <v>0.2365</v>
       </c>
       <c r="H11" t="n">
-        <v>13.9488</v>
+        <v>13.304</v>
       </c>
       <c r="I11" t="n">
-        <v>13.8099</v>
+        <v>13.4035</v>
       </c>
     </row>
     <row r="12">
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0299</v>
+        <v>0.0324</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0308</v>
+        <v>0.0332</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0757</v>
+        <v>0.0797999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0799</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2321</v>
+        <v>0.238</v>
       </c>
       <c r="G12" t="n">
-        <v>0.238</v>
+        <v>0.2238</v>
       </c>
       <c r="H12" t="n">
-        <v>13.8656</v>
+        <v>13.5017</v>
       </c>
       <c r="I12" t="n">
-        <v>14.0604</v>
+        <v>13.3345</v>
       </c>
     </row>
     <row r="13">
@@ -789,28 +789,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0412999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0372999999999999</v>
+        <v>0.0411999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0828999999999999</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07859999999999991</v>
+        <v>0.0786999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2427</v>
+        <v>0.2253</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2339999999999999</v>
+        <v>0.2286</v>
       </c>
       <c r="H13" t="n">
-        <v>13.8761</v>
+        <v>13.2898</v>
       </c>
       <c r="I13" t="n">
-        <v>13.961</v>
+        <v>13.2949</v>
       </c>
     </row>
   </sheetData>
@@ -908,28 +908,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8986784140969158</v>
+        <v>0.8368200836820119</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9090909090909046</v>
+        <v>0.8634361233480213</v>
       </c>
       <c r="D3" t="n">
-        <v>1.213773314203729</v>
+        <v>1.238532110091742</v>
       </c>
       <c r="E3" t="n">
-        <v>1.476510067114094</v>
+        <v>1.38724727838258</v>
       </c>
       <c r="F3" t="n">
-        <v>1.49803536345776</v>
+        <v>1.585444166963967</v>
       </c>
       <c r="G3" t="n">
-        <v>1.584117032392894</v>
+        <v>1.603031396607723</v>
       </c>
       <c r="H3" t="n">
-        <v>1.869752377660077</v>
+        <v>1.934120550332849</v>
       </c>
       <c r="I3" t="n">
-        <v>1.870711725550436</v>
+        <v>1.871420388246526</v>
       </c>
     </row>
     <row r="4">
@@ -937,28 +937,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9444444444444442</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9090909090909046</v>
+        <v>0.7747035573122529</v>
       </c>
       <c r="D4" t="n">
-        <v>1.249630723781387</v>
+        <v>1.273584905660376</v>
       </c>
       <c r="E4" t="n">
-        <v>1.353846153846156</v>
+        <v>1.469522240527181</v>
       </c>
       <c r="F4" t="n">
-        <v>1.915829145728644</v>
+        <v>1.502874535001691</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86546349466776</v>
+        <v>1.650074294205052</v>
       </c>
       <c r="H4" t="n">
-        <v>2.456132858324457</v>
+        <v>1.930032116687762</v>
       </c>
       <c r="I4" t="n">
-        <v>2.451270452774652</v>
+        <v>1.908468195586326</v>
       </c>
     </row>
     <row r="5">
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8127490039840598</v>
+        <v>0.8032128514056226</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8368200836820077</v>
+        <v>0.8305084745762747</v>
       </c>
       <c r="D5" t="n">
-        <v>1.326018808777428</v>
+        <v>1.269592476489027</v>
       </c>
       <c r="E5" t="n">
-        <v>1.444991789819378</v>
+        <v>1.378670788253476</v>
       </c>
       <c r="F5" t="n">
-        <v>2.096700274977085</v>
+        <v>2.005415162454874</v>
       </c>
       <c r="G5" t="n">
-        <v>2.119291705498603</v>
+        <v>2.030164533820841</v>
       </c>
       <c r="H5" t="n">
-        <v>3.416628439504577</v>
+        <v>3.506182495053222</v>
       </c>
       <c r="I5" t="n">
-        <v>3.424474461989674</v>
+        <v>3.484113818055424</v>
       </c>
     </row>
     <row r="6">
@@ -995,28 +995,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7876447876447839</v>
+        <v>0.7874015748031497</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8032128514056185</v>
+        <v>0.7259259259259259</v>
       </c>
       <c r="D6" t="n">
-        <v>1.334384858044164</v>
+        <v>1.227272727272726</v>
       </c>
       <c r="E6" t="n">
-        <v>1.331316187594554</v>
+        <v>1.35562310030395</v>
       </c>
       <c r="F6" t="n">
-        <v>1.960154241645245</v>
+        <v>1.891868880374628</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.986583184257603</v>
       </c>
       <c r="H6" t="n">
-        <v>3.161325113418129</v>
+        <v>3.132561438324098</v>
       </c>
       <c r="I6" t="n">
-        <v>3.217433916168345</v>
+        <v>3.152024298731464</v>
       </c>
     </row>
     <row r="7">
@@ -1024,28 +1024,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7391304347826051</v>
+        <v>0.6802721088435375</v>
       </c>
       <c r="C7" t="n">
-        <v>0.694444444444441</v>
+        <v>0.6689419795221843</v>
       </c>
       <c r="D7" t="n">
-        <v>1.323943661971829</v>
+        <v>1.207153502235468</v>
       </c>
       <c r="E7" t="n">
-        <v>1.262553802008608</v>
+        <v>1.335329341317364</v>
       </c>
       <c r="F7" t="n">
-        <v>1.888155179529509</v>
+        <v>1.900769888793841</v>
       </c>
       <c r="G7" t="n">
-        <v>2.07103825136612</v>
+        <v>1.806425376169174</v>
       </c>
       <c r="H7" t="n">
-        <v>2.895205383429131</v>
+        <v>2.891948031841464</v>
       </c>
       <c r="I7" t="n">
-        <v>3.025632463334491</v>
+        <v>2.898592919248944</v>
       </c>
     </row>
     <row r="8">
@@ -1053,28 +1053,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7786259541984695</v>
+        <v>0.6134969325153375</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7782101167315136</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="D8" t="n">
-        <v>1.131016042780747</v>
+        <v>1.108071135430915</v>
       </c>
       <c r="E8" t="n">
-        <v>1.205479452054796</v>
+        <v>1.221917808219177</v>
       </c>
       <c r="F8" t="n">
-        <v>1.996944565691837</v>
+        <v>2.104166666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>2.071038251366121</v>
+        <v>2.046061722708429</v>
       </c>
       <c r="H8" t="n">
-        <v>2.710914471878468</v>
+        <v>2.70644699745839</v>
       </c>
       <c r="I8" t="n">
-        <v>2.740312844025598</v>
+        <v>2.733429189416992</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7311827956989212</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6920415224913461</v>
+        <v>0.6689419795221843</v>
       </c>
       <c r="D9" t="n">
-        <v>1.134048257372654</v>
+        <v>1.057441253263706</v>
       </c>
       <c r="E9" t="n">
-        <v>1.242937853107345</v>
+        <v>1.298398835516738</v>
       </c>
       <c r="F9" t="n">
-        <v>2.085232452142206</v>
+        <v>1.94061135371179</v>
       </c>
       <c r="G9" t="n">
-        <v>1.945252352437981</v>
+        <v>1.966356795042054</v>
       </c>
       <c r="H9" t="n">
-        <v>3.411881768071972</v>
+        <v>3.516937318584765</v>
       </c>
       <c r="I9" t="n">
-        <v>3.465258230326766</v>
+        <v>3.459273551534546</v>
       </c>
     </row>
     <row r="10">
@@ -1111,28 +1111,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6538461538461507</v>
+        <v>0.6211180124223603</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6644518272425216</v>
+        <v>0.5903614457831325</v>
       </c>
       <c r="D10" t="n">
-        <v>1.146341463414633</v>
+        <v>1.030534351145038</v>
       </c>
       <c r="E10" t="n">
-        <v>1.23943661971831</v>
+        <v>1.145057766367136</v>
       </c>
       <c r="F10" t="n">
-        <v>1.945153061224489</v>
+        <v>2.004510599909788</v>
       </c>
       <c r="G10" t="n">
-        <v>1.931210191082802</v>
+        <v>1.968099246787771</v>
       </c>
       <c r="H10" t="n">
-        <v>3.342896034140238</v>
+        <v>3.441714777054416</v>
       </c>
       <c r="I10" t="n">
-        <v>3.31228157398336</v>
+        <v>3.383611562893178</v>
       </c>
     </row>
     <row r="11">
@@ -1140,28 +1140,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6754966887417185</v>
+        <v>0.5524861878453055</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6269592476488998</v>
+        <v>0.5490196078431387</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9952941176470589</v>
+        <v>1.088709677419354</v>
       </c>
       <c r="E11" t="n">
-        <v>1.113924050632913</v>
+        <v>1.093137254901961</v>
       </c>
       <c r="F11" t="n">
-        <v>1.927939317319848</v>
+        <v>1.922145328719723</v>
       </c>
       <c r="G11" t="n">
-        <v>1.99298860648554</v>
+        <v>1.878224101479915</v>
       </c>
       <c r="H11" t="n">
-        <v>3.257147568249598</v>
+        <v>3.369693325315695</v>
       </c>
       <c r="I11" t="n">
-        <v>3.280501669092463</v>
+        <v>3.290536054015741</v>
       </c>
     </row>
     <row r="12">
@@ -1169,28 +1169,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6822742474916355</v>
+        <v>0.617283950617284</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6493506493506461</v>
+        <v>0.5903614457831325</v>
       </c>
       <c r="D12" t="n">
-        <v>1.117569352708057</v>
+        <v>1.015037593984963</v>
       </c>
       <c r="E12" t="n">
-        <v>1.123882503192848</v>
+        <v>1.116395494367959</v>
       </c>
       <c r="F12" t="n">
-        <v>1.971133132270573</v>
+        <v>1.867226890756303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.910924369747899</v>
+        <v>1.984807864164432</v>
       </c>
       <c r="H12" t="n">
-        <v>3.27669195707362</v>
+        <v>3.320352251938645</v>
       </c>
       <c r="I12" t="n">
-        <v>3.222056271514324</v>
+        <v>3.30756308822978</v>
       </c>
     </row>
     <row r="13">
@@ -1198,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4939467312348657</v>
+        <v>0.447427293064877</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5361930294906153</v>
+        <v>0.4757281553398069</v>
       </c>
       <c r="D13" t="n">
-        <v>1.020506634499397</v>
+        <v>1.003717472118958</v>
       </c>
       <c r="E13" t="n">
-        <v>1.119592875318068</v>
+        <v>1.133418043202033</v>
       </c>
       <c r="F13" t="n">
-        <v>1.885043263288009</v>
+        <v>1.972481136262761</v>
       </c>
       <c r="G13" t="n">
-        <v>1.943589743589744</v>
+        <v>1.943132108486439</v>
       </c>
       <c r="H13" t="n">
-        <v>3.274212494865271</v>
+        <v>3.373293804270945</v>
       </c>
       <c r="I13" t="n">
-        <v>3.244996776735191</v>
+        <v>3.317414948589308</v>
       </c>
     </row>
   </sheetData>
@@ -1317,28 +1317,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4493392070484579</v>
+        <v>0.4184100418410059</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4545454545454523</v>
+        <v>0.4317180616740107</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6068866571018644</v>
+        <v>0.6192660550458708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7382550335570469</v>
+        <v>0.6936236391912901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7490176817288799</v>
+        <v>0.7927220834819836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7920585161964471</v>
+        <v>0.8015156983038614</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9348761888300386</v>
+        <v>0.9670602751664243</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9353558627752178</v>
+        <v>0.9357101941232628</v>
       </c>
     </row>
     <row r="4">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3148148148148147</v>
+        <v>0.2688172043010753</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3030303030303015</v>
+        <v>0.2582345191040843</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4165435745937957</v>
+        <v>0.424528301886792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4512820512820519</v>
+        <v>0.4898407468423938</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6386097152428812</v>
+        <v>0.5009581783338969</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6218211648892534</v>
+        <v>0.5500247647350173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8187109527748192</v>
+        <v>0.6433440388959207</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8170901509248839</v>
+        <v>0.636156065195442</v>
       </c>
     </row>
     <row r="5">
@@ -1375,28 +1375,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.203187250996015</v>
+        <v>0.2008032128514056</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2092050209205019</v>
+        <v>0.2076271186440687</v>
       </c>
       <c r="D5" t="n">
-        <v>0.331504702194357</v>
+        <v>0.3173981191222567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3612479474548446</v>
+        <v>0.3446676970633691</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5241750687442712</v>
+        <v>0.5013537906137184</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5298229263746507</v>
+        <v>0.5075411334552102</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8541571098761441</v>
+        <v>0.8765456237633055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8561186154974184</v>
+        <v>0.871028454513856</v>
       </c>
     </row>
     <row r="6">
@@ -1404,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1575289575289568</v>
+        <v>0.1574803149606299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1606425702811237</v>
+        <v>0.1451851851851852</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2668769716088329</v>
+        <v>0.2454545454545451</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2662632375189107</v>
+        <v>0.27112462006079</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3920308483290489</v>
+        <v>0.3783737760749255</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4</v>
+        <v>0.3973166368515206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6322650226836258</v>
+        <v>0.6265122876648196</v>
       </c>
       <c r="I6" t="n">
-        <v>0.643486783233669</v>
+        <v>0.6304048597462927</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1231884057971008</v>
+        <v>0.1133786848072563</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1157407407407402</v>
+        <v>0.111490329920364</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2206572769953049</v>
+        <v>0.201192250372578</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2104256336681014</v>
+        <v>0.2225548902195607</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3146925299215848</v>
+        <v>0.3167949814656402</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3451730418943533</v>
+        <v>0.3010708960281958</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4825342305715219</v>
+        <v>0.481991338640244</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5042720772224152</v>
+        <v>0.483098819874824</v>
       </c>
     </row>
     <row r="8">
@@ -1462,28 +1462,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1112322791712099</v>
+        <v>0.08764241893076251</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1111728738187877</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1615737203972496</v>
+        <v>0.1582958764901307</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1722113502935423</v>
+        <v>0.1745596868884538</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2852777950988339</v>
+        <v>0.3005952380952381</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2958626073380173</v>
+        <v>0.2922945318154899</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3872734959826382</v>
+        <v>0.3866352853511986</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3914732634322283</v>
+        <v>0.3904898842024275</v>
       </c>
     </row>
     <row r="9">
@@ -1491,28 +1491,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.09139784946236515</v>
+        <v>0.09505703422053231</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08650519031141826</v>
+        <v>0.08361774744027303</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1417560321715818</v>
+        <v>0.1321801566579633</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1553672316384181</v>
+        <v>0.1622998544395923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2606540565177758</v>
+        <v>0.2425764192139738</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2431565440547476</v>
+        <v>0.2457945993802567</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4264852210089965</v>
+        <v>0.4396171648230956</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4331572787908457</v>
+        <v>0.4324091939418182</v>
       </c>
     </row>
     <row r="10">
@@ -1520,28 +1520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07264957264957231</v>
+        <v>0.06901311249137337</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07382798080472462</v>
+        <v>0.06559571619812583</v>
       </c>
       <c r="D10" t="n">
-        <v>0.127371273712737</v>
+        <v>0.1145038167938931</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1377151799687011</v>
+        <v>0.1272286407074596</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2161281179138322</v>
+        <v>0.2227233999899764</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2145789101203114</v>
+        <v>0.2186776940875301</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3714328926822487</v>
+        <v>0.3824127530060462</v>
       </c>
       <c r="I10" t="n">
-        <v>0.368031285998151</v>
+        <v>0.3759568403214642</v>
       </c>
     </row>
     <row r="11">
@@ -1549,28 +1549,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06754966887417185</v>
+        <v>0.05524861878453054</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06269592476488997</v>
+        <v>0.05490196078431388</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09952941176470589</v>
+        <v>0.1088709677419354</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1113924050632913</v>
+        <v>0.1093137254901961</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1927939317319848</v>
+        <v>0.1922145328719723</v>
       </c>
       <c r="G11" t="n">
-        <v>0.199298860648554</v>
+        <v>0.1878224101479916</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3257147568249598</v>
+        <v>0.3369693325315695</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3280501669092463</v>
+        <v>0.3290536054015741</v>
       </c>
     </row>
     <row r="12">
@@ -1578,28 +1578,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06202493159014868</v>
+        <v>0.05611672278338946</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0590318772136951</v>
+        <v>0.05366922234392114</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1015972138825506</v>
+        <v>0.09227614490772386</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1021711366538953</v>
+        <v>0.1014904994879963</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1791939211155066</v>
+        <v>0.1697478991596639</v>
       </c>
       <c r="G12" t="n">
-        <v>0.173720397249809</v>
+        <v>0.1804370785604029</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2978810870066927</v>
+        <v>0.301850204721695</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2929142065013022</v>
+        <v>0.3006875534754345</v>
       </c>
     </row>
     <row r="13">
@@ -1607,28 +1607,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.04116222760290547</v>
+        <v>0.03728560775540642</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04468275245755127</v>
+        <v>0.03964401294498391</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08504221954161639</v>
+        <v>0.08364312267657985</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09329940627650563</v>
+        <v>0.09445150360016945</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1570869386073341</v>
+        <v>0.1643734280218967</v>
       </c>
       <c r="G13" t="n">
-        <v>0.161965811965812</v>
+        <v>0.1619276757072033</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2728510412387726</v>
+        <v>0.2811078170225788</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2704163980612659</v>
+        <v>0.2764512457157757</v>
       </c>
     </row>
   </sheetData>
